--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2665" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2735" uniqueCount="420">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -346,7 +346,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -467,6 +467,38 @@
     <t>Suppliers of different kinds. E.g device suppliers, support suppliers, training suppliers, etc.</t>
   </si>
   <si>
+    <t>Device.extension:registrationToken</t>
+  </si>
+  <si>
+    <t>registrationToken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-device-registrationToken}
+</t>
+  </si>
+  <si>
+    <t>Registration token from the push notification service.</t>
+  </si>
+  <si>
+    <t>Registration token from a push notification service (e.g. FCM/APNs) for the patient's mobile device. Used by telemedicine solutions when sending push notifications.</t>
+  </si>
+  <si>
+    <t>Device.extension:platform</t>
+  </si>
+  <si>
+    <t>platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-device-platform}
+</t>
+  </si>
+  <si>
+    <t>Device platform (iOS/Android).</t>
+  </si>
+  <si>
+    <t>Platform identifier for the patient's mobile device (e.g. iOS, Android). Used together with the registration token to route push notifications via FCM/APNs.</t>
+  </si>
+  <si>
     <t>Device.modifierExtension</t>
   </si>
   <si>
@@ -518,7 +550,7 @@
     <t>Device.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DeviceDefinition)
+    <t xml:space="preserve">Reference(DeviceDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -776,7 +808,7 @@
     <t>The availability status reason of the device.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1087,7 +1119,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1147,7 +1179,7 @@
     <t>Device.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1209,7 +1241,7 @@
     <t>Device.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1297,7 +1329,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1602,12 +1634,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM76"/>
+  <dimension ref="A1:AM78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.09375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1630,7 +1662,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="36.078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="40.71484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2871,43 +2903,41 @@
         <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
       </c>
@@ -2955,7 +2985,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2964,13 +2994,13 @@
         <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>133</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>74</v>
@@ -2981,12 +3011,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>74</v>
       </c>
@@ -2995,7 +3027,7 @@
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -3007,17 +3039,15 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M13" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>156</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
@@ -3066,7 +3096,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -3075,59 +3105,63 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>159</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
@@ -3175,22 +3209,22 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>74</v>
@@ -3201,10 +3235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3224,19 +3258,19 @@
         <v>74</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3286,7 +3320,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3301,13 +3335,13 @@
         <v>94</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
     <row r="16">
@@ -3395,7 +3429,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3407,10 +3441,10 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>74</v>
@@ -3421,14 +3455,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3444,19 +3478,19 @@
         <v>74</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3506,7 +3540,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3518,13 +3552,13 @@
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>74</v>
+        <v>168</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>74</v>
@@ -3539,26 +3573,26 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>182</v>
@@ -3566,12 +3600,8 @@
       <c r="M18" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
       </c>
@@ -3625,16 +3655,16 @@
         <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>74</v>
@@ -3645,21 +3675,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -3668,10 +3698,10 @@
         <v>74</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>187</v>
@@ -3679,7 +3709,9 @@
       <c r="M19" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>74</v>
@@ -3728,68 +3760,72 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>189</v>
-      </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>74</v>
       </c>
@@ -3837,40 +3873,40 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>197</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3886,21 +3922,19 @@
         <v>74</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>201</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
       </c>
@@ -3948,7 +3982,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3963,25 +3997,25 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>74</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3997,20 +4031,18 @@
         <v>74</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -4059,7 +4091,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4074,25 +4106,25 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4108,21 +4140,21 @@
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
@@ -4170,7 +4202,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4185,25 +4217,25 @@
         <v>94</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>215</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4219,21 +4251,21 @@
         <v>74</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>74</v>
       </c>
@@ -4257,13 +4289,13 @@
         <v>74</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>221</v>
+        <v>74</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>222</v>
+        <v>74</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>74</v>
@@ -4281,7 +4313,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4296,29 +4328,29 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>74</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>82</v>
@@ -4327,22 +4359,22 @@
         <v>74</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4368,31 +4400,31 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4407,21 +4439,21 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>74</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4432,7 +4464,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -4444,16 +4476,18 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>233</v>
+        <v>102</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
@@ -4477,13 +4511,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4501,13 +4535,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -4516,10 +4550,10 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>74</v>
+        <v>233</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
@@ -4527,18 +4561,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>82</v>
@@ -4547,22 +4581,22 @@
         <v>74</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4588,13 +4622,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>74</v>
+        <v>238</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4612,7 +4646,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4627,21 +4661,21 @@
         <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>245</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4652,7 +4686,7 @@
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -4664,13 +4698,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>171</v>
+        <v>243</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4697,13 +4731,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>74</v>
+        <v>246</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>74</v>
+        <v>248</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -4721,13 +4755,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -4736,25 +4770,25 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>249</v>
+        <v>74</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4773,15 +4807,17 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>74</v>
@@ -4830,7 +4866,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4848,7 +4884,7 @@
         <v>254</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>255</v>
@@ -4882,7 +4918,7 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>251</v>
+        <v>181</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>257</v>
@@ -4957,18 +4993,18 @@
         <v>259</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>260</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4991,7 +5027,7 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>262</v>
@@ -5048,7 +5084,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5063,21 +5099,21 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>245</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5100,17 +5136,15 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>74</v>
@@ -5159,7 +5193,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5174,21 +5208,21 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>74</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5199,7 +5233,7 @@
         <v>75</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>74</v>
@@ -5211,13 +5245,13 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5268,13 +5302,13 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>74</v>
@@ -5283,21 +5317,21 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>74</v>
+        <v>254</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>74</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5320,15 +5354,17 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>74</v>
@@ -5377,7 +5413,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5389,13 +5425,13 @@
         <v>74</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>175</v>
+        <v>278</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>74</v>
@@ -5403,14 +5439,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5429,17 +5465,15 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>177</v>
+        <v>280</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -5488,7 +5522,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5500,10 +5534,10 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>74</v>
@@ -5514,33 +5548,33 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>182</v>
@@ -5548,12 +5582,8 @@
       <c r="M36" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -5607,16 +5637,16 @@
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>74</v>
@@ -5627,21 +5657,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -5653,15 +5683,17 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>277</v>
+        <v>187</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -5710,22 +5742,22 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>275</v>
+        <v>189</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>74</v>
@@ -5736,42 +5768,46 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5795,13 +5831,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>282</v>
+        <v>74</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>283</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5819,25 +5855,25 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>194</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>284</v>
+        <v>125</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>74</v>
@@ -5852,11 +5888,11 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>82</v>
@@ -5871,13 +5907,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5931,7 +5967,7 @@
         <v>285</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>82</v>
@@ -5943,10 +5979,10 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>74</v>
@@ -5965,7 +6001,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>82</v>
@@ -5980,7 +6016,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>290</v>
@@ -5988,9 +6024,7 @@
       <c r="M40" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>74</v>
@@ -6015,13 +6049,13 @@
         <v>74</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>74</v>
@@ -6042,7 +6076,7 @@
         <v>289</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>82</v>
@@ -6054,10 +6088,10 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>74</v>
@@ -6065,10 +6099,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6091,13 +6125,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6124,29 +6158,31 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6161,10 +6197,10 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>74</v>
+        <v>298</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
@@ -6172,10 +6208,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6186,7 +6222,7 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -6198,15 +6234,17 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>74</v>
@@ -6255,13 +6293,13 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
@@ -6270,10 +6308,10 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>74</v>
@@ -6281,10 +6319,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6307,13 +6345,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>171</v>
+        <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>172</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>173</v>
+        <v>304</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6340,13 +6378,11 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>74</v>
+        <v>305</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -6364,7 +6400,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6376,10 +6412,10 @@
         <v>74</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>74</v>
@@ -6390,14 +6426,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6416,17 +6452,15 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>177</v>
+        <v>307</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -6475,7 +6509,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>179</v>
+        <v>306</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6487,10 +6521,10 @@
         <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>74</v>
@@ -6501,33 +6535,33 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>182</v>
@@ -6535,12 +6569,8 @@
       <c r="M45" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -6594,16 +6624,16 @@
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>74</v>
@@ -6614,21 +6644,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
@@ -6640,15 +6670,17 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>303</v>
+        <v>187</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>74</v>
@@ -6697,22 +6729,22 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>74</v>
@@ -6723,42 +6755,46 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>74</v>
       </c>
@@ -6806,25 +6842,25 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>194</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>74</v>
@@ -6832,21 +6868,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -6858,13 +6894,13 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6915,13 +6951,13 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>74</v>
@@ -6941,10 +6977,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6967,13 +7003,13 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>172</v>
+        <v>316</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7024,7 +7060,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>174</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7036,13 +7072,13 @@
         <v>74</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>74</v>
@@ -7050,14 +7086,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7076,17 +7112,15 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>177</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -7135,7 +7169,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7147,10 +7181,10 @@
         <v>74</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>74</v>
@@ -7161,33 +7195,33 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>182</v>
@@ -7195,12 +7229,8 @@
       <c r="M51" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N51" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>74</v>
       </c>
@@ -7254,16 +7284,16 @@
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>74</v>
@@ -7274,21 +7304,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -7300,15 +7330,17 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>315</v>
+        <v>187</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>74</v>
@@ -7357,22 +7389,22 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>314</v>
+        <v>189</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>74</v>
@@ -7383,42 +7415,46 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>318</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>74</v>
       </c>
@@ -7466,25 +7502,25 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>317</v>
+        <v>194</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>74</v>
@@ -7492,18 +7528,18 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>74</v>
+        <v>286</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>82</v>
@@ -7518,13 +7554,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>171</v>
+        <v>243</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7575,10 +7611,10 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>82</v>
@@ -7601,10 +7637,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7615,7 +7651,7 @@
         <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -7627,13 +7663,13 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7684,13 +7720,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -7702,7 +7738,7 @@
         <v>74</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>74</v>
@@ -7710,10 +7746,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7721,7 +7757,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>82</v>
@@ -7736,13 +7772,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7793,10 +7829,10 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>174</v>
+        <v>330</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>82</v>
@@ -7805,10 +7841,10 @@
         <v>74</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>74</v>
@@ -7819,14 +7855,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7845,17 +7881,15 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>177</v>
+        <v>334</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>74</v>
@@ -7904,7 +7938,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>179</v>
+        <v>333</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7916,10 +7950,10 @@
         <v>74</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>74</v>
@@ -7930,33 +7964,33 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>182</v>
@@ -7964,12 +7998,8 @@
       <c r="M58" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>74</v>
       </c>
@@ -8023,16 +8053,16 @@
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>74</v>
@@ -8043,21 +8073,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -8069,15 +8099,17 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>330</v>
+        <v>187</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>74</v>
@@ -8126,22 +8158,22 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>329</v>
+        <v>189</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>74</v>
@@ -8152,14 +8184,14 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>74</v>
+        <v>191</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8172,22 +8204,26 @@
         <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>333</v>
+        <v>127</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>334</v>
+        <v>192</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>74</v>
       </c>
@@ -8235,7 +8271,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>332</v>
+        <v>194</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8247,10 +8283,10 @@
         <v>74</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8261,10 +8297,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8272,10 +8308,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -8287,13 +8323,13 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8344,13 +8380,13 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
@@ -8370,10 +8406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8384,7 +8420,7 @@
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8396,18 +8432,16 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
       </c>
@@ -8455,13 +8489,13 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>74</v>
@@ -8470,10 +8504,10 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>344</v>
+        <v>74</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>345</v>
+        <v>74</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>74</v>
@@ -8495,7 +8529,7 @@
         <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -8507,13 +8541,13 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8570,7 +8604,7 @@
         <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -8579,10 +8613,10 @@
         <v>94</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>350</v>
+        <v>74</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>351</v>
+        <v>74</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
@@ -8590,10 +8624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8604,7 +8638,7 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -8616,18 +8650,18 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L64" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>74</v>
       </c>
@@ -8675,13 +8709,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -8690,10 +8724,10 @@
         <v>94</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -8701,10 +8735,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8727,18 +8761,16 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>361</v>
-      </c>
       <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>362</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>74</v>
       </c>
@@ -8786,7 +8818,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8801,10 +8833,10 @@
         <v>94</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
@@ -8812,10 +8844,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8826,7 +8858,7 @@
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8838,16 +8870,16 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>96</v>
+        <v>363</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8897,13 +8929,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8912,10 +8944,10 @@
         <v>94</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
@@ -8923,10 +8955,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8937,7 +8969,7 @@
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>74</v>
@@ -8949,16 +8981,18 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>74</v>
       </c>
@@ -9006,13 +9040,13 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>74</v>
@@ -9021,10 +9055,10 @@
         <v>94</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9058,15 +9092,17 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>172</v>
+        <v>376</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>74</v>
@@ -9115,7 +9151,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>174</v>
+        <v>375</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9127,13 +9163,13 @@
         <v>74</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>175</v>
+        <v>379</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>74</v>
+        <v>374</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>74</v>
@@ -9141,14 +9177,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9167,17 +9203,15 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>127</v>
+        <v>381</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>177</v>
+        <v>382</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>74</v>
@@ -9214,19 +9248,19 @@
         <v>74</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>179</v>
+        <v>380</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9238,10 +9272,10 @@
         <v>74</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>175</v>
+        <v>384</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9252,10 +9286,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9275,20 +9309,18 @@
         <v>74</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>379</v>
+        <v>181</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>380</v>
+        <v>182</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>74</v>
@@ -9325,17 +9357,19 @@
         <v>74</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AC70" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>384</v>
+        <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>385</v>
+        <v>184</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9347,10 +9381,10 @@
         <v>74</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>386</v>
+        <v>185</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
@@ -9361,23 +9395,21 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -9386,19 +9418,19 @@
         <v>74</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>389</v>
+        <v>127</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>380</v>
+        <v>187</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>381</v>
+        <v>188</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>382</v>
+        <v>159</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9436,34 +9468,34 @@
         <v>74</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>74</v>
+        <v>387</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>385</v>
+        <v>189</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>386</v>
+        <v>185</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>74</v>
@@ -9474,14 +9506,12 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
@@ -9502,16 +9532,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>171</v>
+        <v>389</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9549,19 +9579,17 @@
         <v>74</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="AC72" s="2"/>
       <c r="AD72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>74</v>
+        <v>394</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9576,7 +9604,7 @@
         <v>94</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>74</v>
@@ -9587,12 +9615,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
@@ -9613,15 +9643,17 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>251</v>
+        <v>399</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>74</v>
@@ -9696,18 +9728,20 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C74" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>82</v>
@@ -9722,15 +9756,17 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>398</v>
+        <v>181</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>74</v>
@@ -9779,10 +9815,10 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>82</v>
@@ -9794,7 +9830,7 @@
         <v>94</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>74</v>
@@ -9805,10 +9841,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9819,7 +9855,7 @@
         <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -9831,13 +9867,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>233</v>
+        <v>261</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9888,13 +9924,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -9903,7 +9939,7 @@
         <v>94</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>223</v>
+        <v>406</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>74</v>
@@ -9914,10 +9950,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9925,7 +9961,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>82</v>
@@ -9937,16 +9973,16 @@
         <v>74</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9997,10 +10033,10 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>82</v>
@@ -10012,12 +10048,230 @@
         <v>94</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>74</v>
+        <v>412</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-device.xlsx
+++ b/fhir/StructureDefinition-ehealth-device.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
